--- a/src/attributions/attributions_ig_traj_331.xlsx
+++ b/src/attributions/attributions_ig_traj_331.xlsx
@@ -1568,37 +1568,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03251932444394178</v>
+        <v>-0.02518327424933632</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3438926662425554</v>
+        <v>0.03082365623308234</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03496782482494351</v>
+        <v>0.005986459789148772</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.06495335735067174</v>
+        <v>-0.02168677196659175</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3171791814450751</v>
+        <v>0.0550127479222724</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.07138920335935367</v>
+        <v>-0.01323402690094206</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1622,133 +1622,133 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04730531920587148</v>
+        <v>0.01965560488704341</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2832908335249125</v>
+        <v>0.02084548275719659</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3258450493238491</v>
+        <v>0.004671348810829967</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1465891513053214</v>
+        <v>0.01562115329376884</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1852710821792396</v>
+        <v>0.006560040798525176</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.2423370592677605</v>
+        <v>-0.02564428580747481</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.09988119128640083</v>
+        <v>0.005761181620913874</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1605443036792489</v>
+        <v>0.02308091832044568</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.132943501550913</v>
+        <v>0.02747071872690036</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07823862876536349</v>
+        <v>-0.02777600005044933</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.6969619958214756</v>
+        <v>0.1041634473480327</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4879599551311475</v>
+        <v>-0.02242469211801532</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01531895131688642</v>
+        <v>-0.01749095023945612</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01450773360866885</v>
+        <v>-0.01399260425956824</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.1974355363456081</v>
+        <v>-0.01598481904031986</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,25 +1757,25 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01682815961057959</v>
+        <v>0.01112291215511075</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1479255158465394</v>
+        <v>0.03246920601550452</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1746805573615625</v>
+        <v>0.03314358617530958</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,37 +1784,37 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.07158859353022071</v>
+        <v>0.0001418968043312794</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.3732576566925022</v>
+        <v>0.07948659691382934</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2121322970386049</v>
+        <v>0.02258646578696201</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0001670831278045757</v>
+        <v>0.01507082289918677</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.2055786465459877</v>
+        <v>-0.02860329317095614</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
@@ -1823,13 +1823,13 @@
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01676342481433708</v>
+        <v>-0.0111686090938867</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
@@ -1838,49 +1838,49 @@
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.0857737231637927</v>
+        <v>-0.008641841897852416</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.01628502770677764</v>
+        <v>-0.02877030708580279</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1137766615583274</v>
+        <v>-0.009558715344273293</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.009016019336861773</v>
+        <v>0.00516667237934286</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.2129803787612637</v>
+        <v>-0.03088172521556704</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.01848126470576252</v>
+        <v>-0.02149682569864893</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1892,46 +1892,46 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.0204573734371791</v>
+        <v>-0.004789245174893719</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1680131783848771</v>
+        <v>-0.05284416263520444</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02478030695359772</v>
+        <v>-0.02144354656614104</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.04294086420556908</v>
+        <v>-0.002895644465465086</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.08687681041264883</v>
+        <v>-0.01124307077496029</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1573622307977608</v>
+        <v>-0.01504772181520344</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,31 +1940,31 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.02018107324320145</v>
+        <v>0.009828420594351342</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.3034953611696145</v>
+        <v>-0.05316863667287271</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.04781332367274259</v>
+        <v>-0.0249162184407207</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
@@ -1973,64 +1973,64 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.03624045786711472</v>
+        <v>0.007539244999870807</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.07674780666979186</v>
+        <v>0.004582388967986236</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1086994090259837</v>
+        <v>-0.02369449535534135</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.009429540513998703</v>
+        <v>0.002913831587363996</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.23158298179307</v>
+        <v>-0.008862570544400117</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.05466045068413791</v>
+        <v>-0.01304465376204543</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.04791183586750479</v>
+        <v>0.01072021887683374</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.2300495963749399</v>
+        <v>-0.0451772493618465</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,13 +2039,13 @@
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.03502101527797568</v>
+        <v>-0.02028871174258408</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03523106563787719</v>
+        <v>0.01795022566013896</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.07355293290813626</v>
+        <v>0.02399420362815606</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,10 +2066,10 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.09722941492664995</v>
+        <v>-0.008765802333136251</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2078,61 +2078,61 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.05704126934370282</v>
+        <v>0.0502667128751552</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.194486262969876</v>
+        <v>-0.007950923958402871</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.08514181213767234</v>
+        <v>0.04055844546737656</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.1075233348076856</v>
+        <v>0.03582790091162395</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.1377038547159989</v>
+        <v>-0.02550515634417064</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,157 +2709,157 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3775215384978758</v>
+        <v>0.319992776077367</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09460017079860968</v>
+        <v>-0.1617635422372382</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01837624704309709</v>
+        <v>-0.07086386987126073</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2825335756898309</v>
+        <v>0.3201860324152729</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1548587573022387</v>
+        <v>-0.3024835487002968</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03098169435210578</v>
+        <v>-0.1425749368364119</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1947311591083854</v>
+        <v>0.1534617923479874</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0001594001238532104</v>
+        <v>-0.02121287675602207</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06245043481046523</v>
+        <v>-0.02703882896597181</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1431054779939783</v>
+        <v>-0.0939653864131961</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.04445321966006026</v>
+        <v>-0.2583530812114139</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.04329517923311742</v>
+        <v>-0.1197413807978235</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03915034782149171</v>
+        <v>0.1873236260714927</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.1121934358066897</v>
+        <v>-0.06957998671853878</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.0810768533837815</v>
+        <v>0.0864822542095512</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5297729728225447</v>
+        <v>0.5092223600878147</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.00143688470537283</v>
+        <v>-0.2464511950731319</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.29844345712971</v>
+        <v>-0.3836751193054582</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
@@ -2868,106 +2868,106 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.07117388511597909</v>
+        <v>0.08225674952157283</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.129409152007595</v>
+        <v>-0.1349422506783745</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1491741968750437</v>
+        <v>-0.01026913791982322</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06798933110311733</v>
+        <v>0.005541862287393119</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.995529886668329e-10</v>
+        <v>1.028775848183452e-10</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2274912792919971</v>
+        <v>0.04519314726489455</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2734969097174096</v>
+        <v>0.4527851162546307</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01544388392072348</v>
+        <v>-0.1674566632671698</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1136313833720909</v>
+        <v>-0.07913145731700895</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.164294848971003</v>
+        <v>-0.1724951680752573</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01986372251663777</v>
+        <v>0.1921722805812887</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.03736151745999557</v>
+        <v>0.01104127506464536</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,19 +2979,19 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0120847443419968</v>
+        <v>-0.1318391132026085</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06176644243765889</v>
+        <v>0.1055555090628465</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.08039940440160426</v>
+        <v>0.04072500511439665</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
@@ -3000,28 +3000,28 @@
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1567389261857122</v>
+        <v>-0.1840296708839742</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.05213467655827858</v>
+        <v>0.2057516779825997</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04607983627337604</v>
+        <v>0.02136380659019125</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1161508345784289</v>
+        <v>-0.2074589050627358</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01943161839434206</v>
+        <v>0.2210552858238245</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.07260902419309763</v>
+        <v>0.02758927758981828</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3051,112 +3051,112 @@
         <v>-0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.03336469871341385</v>
+        <v>-0.07179451300704379</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.1356975904042493</v>
+        <v>0.04956726464007153</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.04031294016564397</v>
+        <v>0.06198642222601741</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1049886800564138</v>
+        <v>0.038597144545496</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.009020251031152933</v>
+        <v>0.1521531841920003</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.04779938955680858</v>
+        <v>-0.06054500285223137</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1103098637287269</v>
+        <v>-0.125776982423606</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03413677029259439</v>
+        <v>0.170174781698834</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04458421952900096</v>
+        <v>0.008760648998716557</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1538850148868556</v>
+        <v>-0.1641907195548669</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1296178548789068</v>
+        <v>-0.1235113663020211</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1193402870555895</v>
+        <v>-0.07644599381121879</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1655838152099972</v>
+        <v>-0.2128161029415919</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01763855911975289</v>
+        <v>0.2261370425510903</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04257069629501704</v>
+        <v>-0.01105183595719638</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
@@ -3195,49 +3195,49 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01747771349007303</v>
+        <v>-0.1198593240157315</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.05667368469784145</v>
+        <v>0.09222184150015966</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01198227001613248</v>
+        <v>-0.04616951535517202</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.004477539830241762</v>
+        <v>-0.0554389068850293</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.06858401608841425</v>
+        <v>0.249968457391314</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0314837908503823</v>
+        <v>0.3549436994235002</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,28 +3246,28 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.003587034543148954</v>
+        <v>-0.146491863266957</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.08710643806842586</v>
+        <v>0.07479256648147817</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,37 +3275,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.08549065093912959</v>
+        <v>-0.01082733578290131</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2023429885183032</v>
+        <v>0.03613789732554656</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02881761411873576</v>
+        <v>-0.004936488554450165</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.07563821318162901</v>
+        <v>-0.008647880364909061</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1781208461486853</v>
+        <v>0.04862415644432681</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07795694740588394</v>
+        <v>-0.01307945084147286</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3329,52 +3329,52 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01249093933676193</v>
+        <v>0.00802384130824808</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2171923621267428</v>
+        <v>0.008652241314051113</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.139841902326209</v>
+        <v>-0.005102117171567267</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1198118050443587</v>
+        <v>-0.003628577829050968</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2032836191981855</v>
+        <v>-0.003280799203414912</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.003441171302531628</v>
+        <v>-0.004808978484752605</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,37 +3383,37 @@
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.009472120773432685</v>
+        <v>-0.002808683989168873</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1165043566741882</v>
+        <v>0.01711789018509348</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0794233588265008</v>
+        <v>0.007447926969123731</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.05335207860660674</v>
+        <v>-0.009196614155306886</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3255570418780296</v>
+        <v>0.05042175501327976</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,25 +3422,25 @@
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3129620663428202</v>
+        <v>-0.01439248279247109</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.06156106743026009</v>
+        <v>-0.008340411717957559</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.06393516140053783</v>
+        <v>0.008738134168746522</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.203860447302236</v>
+        <v>-0.008421157663332783</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.04204089362199951</v>
+        <v>-0.005890507031460952</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1261650985831942</v>
+        <v>-0.001915535159149167</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0473587994575087</v>
+        <v>0.02186908249744593</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,25 +3491,25 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.04445843075534905</v>
+        <v>0.004401871695296346</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.24877848118218</v>
+        <v>0.04051094256007307</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1161779066888605</v>
+        <v>-0.001442873500415593</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3518,76 +3518,76 @@
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0266857983015669</v>
+        <v>0.007669663913084873</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.09525130946993135</v>
+        <v>-0.02033688398575842</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.002559860192863072</v>
+        <v>0.001861546378634638</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.03669317346733476</v>
+        <v>-3.63052504845907e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.007412226823505213</v>
+        <v>-0.01528821576786079</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0660633453632762</v>
+        <v>0.004038921224746347</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.01275492670602578</v>
+        <v>0.004571170913616279</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.09978718110066165</v>
+        <v>-0.02001174397213518</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.011163443815762</v>
+        <v>0.001444734614746881</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.01819076473146449</v>
+        <v>-0.001917109202135822</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.1776066875365628</v>
+        <v>-0.02083053022167918</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,25 +3611,25 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07800982848653998</v>
+        <v>-0.005565758069513298</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01434522789658644</v>
+        <v>0.002800282368983061</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.04099395633608321</v>
+        <v>-0.01527782382025118</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
@@ -3638,25 +3638,25 @@
         <v>-0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03171552878235563</v>
+        <v>0.002388616083197519</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0003976261696203298</v>
+        <v>0.01263553741684104</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.1018391103741961</v>
+        <v>0.01178331906681098</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,25 +3665,25 @@
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.005827318585311494</v>
+        <v>0.001391342323397508</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.03634575888481029</v>
+        <v>-0.0001662046571395736</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001549288944785051</v>
+        <v>-0.01207070417013564</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0008341770506632497</v>
+        <v>-0.008295341290315813</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,52 +3707,52 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0.02952123964422742</v>
+        <v>0.0008602837264789498</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1176236999129197</v>
+        <v>-0.006110432662683843</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.007457642366944456</v>
+        <v>-0.002473439007557359</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.00953931721135258</v>
+        <v>0.007016357070482211</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1074491410421499</v>
+        <v>-0.02281155904970269</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05331455325086647</v>
+        <v>-0.001509873135637613</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.04597648835367252</v>
+        <v>-0.002084203382387594</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.03276422777927891</v>
+        <v>-0.01164609375889729</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,7 +3773,7 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.08412738562164464</v>
+        <v>0.007723236329605299</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
@@ -3788,10 +3788,10 @@
         <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0.003244236674797563</v>
+        <v>0.02527390141217432</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.1724566414505363</v>
+        <v>-0.011872191372644</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1402595367211871</v>
+        <v>0.004152644624970414</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0.0714047435437033</v>
+        <v>0.01223602009847749</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02949661157333354</v>
+        <v>-0.01413089367287265</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,24 +3839,24 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3948980889289234</v>
+        <v>0.6036564660840756</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1740502108928731</v>
+        <v>-0.4131325998850761</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08867798168150165</v>
+        <v>-0.1893467339558759</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3017043154052031</v>
+        <v>0.5428701177261682</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1854228438243722</v>
+        <v>-0.6642646198221911</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1203821309888043</v>
+        <v>-0.3100148193460469</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1300217999422623</v>
+        <v>0.2302117388022183</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01650614149336327</v>
+        <v>-0.03050812940390208</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06356894548052225</v>
+        <v>-0.009534601366342876</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3928,22 +3928,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1023209534216799</v>
+        <v>0.0525180075276644</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.009151879950970309</v>
+        <v>-0.1937293249849439</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.05789353168634009</v>
+        <v>-0.01613915620581494</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3952,73 +3952,73 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.07819369372404204</v>
+        <v>0.3637916550730942</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.09223176637026473</v>
+        <v>-0.03642813637664877</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.04112244514449354</v>
+        <v>0.3197829082956323</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.6262088275900496</v>
+        <v>0.9320191944153219</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.05895686484566786</v>
+        <v>-0.4515520160162453</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1397120751299656</v>
+        <v>-0.3604378596443405</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01566195346220936</v>
+        <v>-0.07728456919830538</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.09164706799253079</v>
+        <v>-0.08637604806599511</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1815191560711841</v>
+        <v>-0.1091897570526139</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02244564511735795</v>
+        <v>-0.1087299393553046</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1062767066069583</v>
+        <v>0.02303015886493231</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08344362719736385</v>
+        <v>0.1365025043733868</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,43 +4063,43 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.3263424715754533</v>
+        <v>0.699769702886579</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.01658826593165637</v>
+        <v>-0.3470826123617962</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.05150974251242511</v>
+        <v>-0.1042279765392613</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1313712105334076</v>
+        <v>-0.3281804082116611</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05773938177373392</v>
+        <v>0.2319309218792633</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02731118129591807</v>
+        <v>0.04778754055940878</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.002861944910056625</v>
+        <v>-0.206780823870379</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.04289427003566889</v>
+        <v>0.09904960742468323</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1133648385948384</v>
+        <v>0.06469460654028408</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,58 +4138,58 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1229352478178216</v>
+        <v>-0.3619890128819546</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.08522141481563167</v>
+        <v>0.2493267277365988</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02110608829588588</v>
+        <v>0.0866391620150522</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.08665825667005286</v>
+        <v>-0.4610035168841982</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1058243280150816</v>
+        <v>0.3424812721082534</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.1050852129612996</v>
+        <v>-0.1189859356331582</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07181201243863457</v>
+        <v>-0.1324218927873102</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.01407975474459789</v>
+        <v>0.1332347772112131</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.04323636068918125</v>
+        <v>-0.09410716762868396</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4222,28 +4222,28 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03822815466232457</v>
+        <v>0.1719059780226695</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.02514894552257554</v>
+        <v>0.1658440996293743</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01543806946197377</v>
+        <v>-0.05574539592365404</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,16 +4252,16 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1215374286785858</v>
+        <v>-0.2391213263454622</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07126864489985905</v>
+        <v>0.1962033399519333</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1125412624679556</v>
+        <v>0.08827747426530586</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,7 +4270,7 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08256899678866643</v>
+        <v>-0.3078671212598271</v>
       </c>
       <c r="EQ7" t="n">
         <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1128777995850468</v>
+        <v>0.1827876546196995</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1071327848010282</v>
+        <v>0.004972000646450401</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,100 +4306,100 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1297550963930703</v>
+        <v>-0.3973118053920373</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.08349247375261724</v>
+        <v>0.2749873527798726</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03987560294647597</v>
+        <v>0.05234591140094323</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03091826955054853</v>
+        <v>-0.1444536760692721</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.02786477983972563</v>
+        <v>0.0156772221252193</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.002817318655721576</v>
+        <v>0.06737505866611251</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03415082181151265</v>
+        <v>-0.3276411505207762</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.130268402562481</v>
+        <v>0.526479570012245</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1298692788610069</v>
+        <v>0.1338278276509541</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03847983017309826</v>
+        <v>-0.2796543798415127</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.02625067997094474</v>
+        <v>0.1075981072784149</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4413,10 +4413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1311470284758748</v>
+        <v>0.5033387130055813</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03134895595989717</v>
+        <v>-0.01064363906802337</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08041425267108071</v>
+        <v>-0.3111485143641413</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,13 +4437,13 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09550588192842238</v>
+        <v>0.539512175010966</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02295238113438983</v>
+        <v>-0.1786719060639952</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08856604028848199</v>
+        <v>-0.3477694204606214</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
@@ -4467,52 +4467,52 @@
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02700056578363953</v>
+        <v>0.008156496557423745</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02718052275288665</v>
+        <v>-0.1156430054150715</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.003876414734385414</v>
+        <v>-0.1598025848837596</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03298249923987621</v>
+        <v>0.1784517323117488</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0109638299378031</v>
+        <v>-0.1418902658697508</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.02221318357016916</v>
+        <v>0.01366499580029535</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,19 +4524,19 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01941547822832968</v>
+        <v>0.1773607211749111</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.005132734164230103</v>
+        <v>0.02567648366568845</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05384822853363077</v>
+        <v>-0.1699201883280094</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1466983374704059</v>
+        <v>0.9252758004050768</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01861628045028027</v>
+        <v>-0.2596937260867241</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1219060540057028</v>
+        <v>-0.4054364567078518</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05177251028414887</v>
+        <v>0.05060708767306074</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,40 +4587,40 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04491245118168984</v>
+        <v>-0.02124559436900178</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.02853089421309058</v>
+        <v>-0.1581230042010445</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03810467039438268</v>
+        <v>0.1070170327994766</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02201528756365864</v>
+        <v>0.1393045590899064</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01619918781277331</v>
+        <v>0.1012909405289213</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
@@ -4629,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07921992035623786</v>
+        <v>0.4742326768612391</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.007885248851542081</v>
+        <v>-0.1245453899822748</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.04783961806179107</v>
+        <v>-0.3799366105740586</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4656,76 +4656,76 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.03841211058213765</v>
+        <v>-0.2960116683186851</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>4.639407001919957e-05</v>
+        <v>-0.0180292408143307</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03517595369341046</v>
+        <v>0.2084360527156437</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.008403295761704337</v>
+        <v>-0.2650632013536846</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.002268201958172793</v>
+        <v>0.05988553627057329</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.007312311189866271</v>
+        <v>0.1205634708428103</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03183659978332622</v>
+        <v>-0.2775943791521933</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0005021630893029596</v>
+        <v>-0.01476790095621162</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0413862699782641</v>
+        <v>0.1917367824212985</v>
       </c>
       <c r="DB8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.02843287182340999</v>
+        <v>-0.1015053747293368</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05368401318292124</v>
+        <v>-0.1661996494585925</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01585540579069115</v>
+        <v>0.1634327277743975</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,31 +4761,31 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.006554268210559047</v>
+        <v>-0.07996589732102589</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02183234667290458</v>
+        <v>-0.01048980086216281</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01499361230265445</v>
+        <v>0.0684350692931</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
@@ -4794,19 +4794,19 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.03431574802249247</v>
+        <v>0.1709401205176686</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01947664027407229</v>
+        <v>0.006224498466175727</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.01013112500033002</v>
+        <v>0.01569074139394284</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4815,121 +4815,121 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.0276713896767866</v>
+        <v>-0.1172426525310419</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.008076641117176882</v>
+        <v>-0.08205222426639903</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.022652201165023</v>
+        <v>0.1735590650189088</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.02054595238644313</v>
+        <v>-0.1836679037998088</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.002109964970694648</v>
+        <v>-0.1375144305006703</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01730122447089783</v>
+        <v>0.1378821085196377</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.0334467879417267</v>
+        <v>-0.3039258698925039</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.003756130012583553</v>
+        <v>-0.06289915946915359</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03851342972156284</v>
+        <v>0.1969871092720456</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02104637199650531</v>
+        <v>-0.1916692785047379</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03002349287780976</v>
+        <v>0.07483313386440904</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03786204686279608</v>
+        <v>0.200251153417681</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.02791305203686751</v>
+        <v>-0.1128967529324851</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,63 +4938,63 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.008373187178959348</v>
+        <v>0.0599505089998856</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.003090746937206496</v>
+        <v>0.02661067791852942</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02610521004527848</v>
+        <v>-0.1215759987539752</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02366858393662821</v>
+        <v>0.1012053022782486</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3629992948746502</v>
+        <v>0.59681340409009</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09843947419004506</v>
+        <v>-0.2787453989365252</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06033032646433827</v>
+        <v>-0.1783943946749456</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5006,22 +5006,22 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2460453791278457</v>
+        <v>0.5252368380959088</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1029145230359791</v>
+        <v>-0.482179880788594</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08068801364553647</v>
+        <v>-0.2629718295513493</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,28 +5030,28 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1060768476385678</v>
+        <v>0.197389380674514</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.03508420216012582</v>
+        <v>0.0367160353717994</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02281937228567449</v>
+        <v>-0.08969493630651536</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5063,100 +5063,100 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07054107440385241</v>
+        <v>0.04720733546733968</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01999017648118179</v>
+        <v>-0.1270751673283473</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.05784126368888541</v>
+        <v>-0.1349002509770267</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0530577346282945</v>
+        <v>0.2796374996019186</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03505366566428678</v>
+        <v>0.03154800156133877</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05925070623670553</v>
+        <v>0.08055240979296172</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4653046895302342</v>
+        <v>0.6783348211205976</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.0577187557342933</v>
+        <v>-0.344639734349346</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08626915334672466</v>
+        <v>-0.4700900600824426</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0506198906237716</v>
+        <v>0.04550104980890172</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06555036498833354</v>
+        <v>-0.122880576029763</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1524806036185816</v>
+        <v>-0.0298490782863544</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0812192862351433</v>
+        <v>-0.00153252884882236</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.07856996475380053</v>
+        <v>0.09368986243195203</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.09594897101958694</v>
+        <v>0.1465342741756497</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2496150057365549</v>
+        <v>0.5504288731589398</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.032005136501742</v>
+        <v>-0.2630652251276135</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01565307708409762</v>
+        <v>-0.1528633480116437</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5225,19 +5225,19 @@
         <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.09723990561491971</v>
+        <v>-0.2311590711484663</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0353470940056947</v>
+        <v>0.2568275782401966</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01739678796668411</v>
+        <v>0.0445314481605666</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5249,25 +5249,25 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.01122865796865931</v>
+        <v>-0.1409320682341473</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.01035180994477812</v>
+        <v>0.0279143826481903</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.05751465494921092</v>
+        <v>0.03695686123002384</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,55 +5276,55 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.09071480846873059</v>
+        <v>-0.2484341592621881</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.05737371817360408</v>
+        <v>0.2658037848939961</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02361467142813971</v>
+        <v>0.04796769448344704</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.07050370874462043</v>
+        <v>-0.243521376369278</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1698399706376202</v>
+        <v>0.1737481385626822</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01629079350553512</v>
+        <v>-0.0466446523541157</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,19 +5336,19 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06131588489345986</v>
+        <v>-0.1402462808315752</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.03515773888997505</v>
+        <v>0.1312558969892404</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02074634147054091</v>
+        <v>-0.1559678984691415</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5363,22 +5363,22 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03755599280244309</v>
+        <v>0.07172642299033023</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.02493832144355154</v>
+        <v>0.173898347288213</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02523919192784797</v>
+        <v>-0.08591062537827289</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5390,25 +5390,25 @@
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07465090238060434</v>
+        <v>-0.1263444015153456</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.08863154978300078</v>
+        <v>-0.3261437469037246</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03671816841225122</v>
+        <v>0.03484352474686504</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07746877673009528</v>
+        <v>-0.2130377571997983</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.06558205699425958</v>
+        <v>0.1550037342335334</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.0315903712509674</v>
+        <v>-0.03650449143124747</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,76 +5441,76 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08869310185263275</v>
+        <v>-0.2800078104509284</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.05983880359726301</v>
+        <v>0.2762095204365639</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02574893837492392</v>
+        <v>0.02612896044535886</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.009938525374253888</v>
+        <v>-0.08192437844523857</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.02432709789566853</v>
+        <v>-0.07451642291799189</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.02638065225951762</v>
+        <v>0.134633633566839</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.003995899038994031</v>
+        <v>-0.1749940682867542</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0181059294222145</v>
+        <v>0.4520798635582945</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.03943193679969166</v>
+        <v>0.1828915610821926</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.0236306823015286</v>
+        <v>-0.1857700503349697</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.01833117156871093</v>
+        <v>0.08540628140050689</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5551,214 +5551,214 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.04721763183016317</v>
+        <v>-0.1202922074074713</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1543917161172184</v>
+        <v>0.08147706975595871</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08592446198559817</v>
+        <v>-0.01153902562289546</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04665564228505617</v>
+        <v>-0.001720054970786805</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0002181285956789655</v>
+        <v>-0.1253248887807811</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1002024324230659</v>
+        <v>0.0431124180864623</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02695366348752834</v>
+        <v>-0.1449581378253422</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.04455246509207006</v>
+        <v>-0.04282047660708616</v>
       </c>
       <c r="Q10" t="n">
         <v>-0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03414693819779742</v>
+        <v>0.1308642492282749</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07527535323791922</v>
+        <v>-0.03850931901362149</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05699846557730361</v>
+        <v>-0.05862384312857195</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.0548044609964967</v>
+        <v>0.01813779741032351</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.02663774473418924</v>
+        <v>0.1491989027678881</v>
       </c>
       <c r="AC10" t="n">
         <v>-0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.06733132177063354</v>
+        <v>-0.2212098892981073</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03837364438148697</v>
+        <v>-0.3546704038134276</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.01673705563947327</v>
+        <v>-0.04630116497297465</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0003630463619830569</v>
+        <v>0.01816643995324726</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.03612820634334617</v>
+        <v>-0.086929983150819</v>
       </c>
       <c r="AN10" t="n">
         <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.02184316150024498</v>
+        <v>-0.1746765932196336</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.01016348716835931</v>
+        <v>0.04920431958354635</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.04328688936867071</v>
+        <v>-0.07530067857485456</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2190436371728998</v>
+        <v>0.07014270535163893</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2988304772238866</v>
+        <v>-0.3691827319347331</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.01896773321960068</v>
+        <v>0.1034483372607059</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.07214474535715862</v>
+        <v>-0.03405071222889874</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.01916570130576715</v>
+        <v>-0.08637813611086959</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.01407073035435497</v>
+        <v>0.1702088541734366</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.04267843095970511</v>
+        <v>-0.1303764041628529</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.003335532197343382</v>
+        <v>0.1017301273212531</v>
       </c>
       <c r="BM10" t="n">
         <v>-0</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1076856307091064</v>
+        <v>0.1515955401677413</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.04823576941403537</v>
+        <v>0.1061381721704973</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.02813168977080944</v>
+        <v>0.005063181262232999</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,25 +5767,25 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.0217444663010062</v>
+        <v>0.05143121383573446</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.05732665217720135</v>
+        <v>0.1181713594688616</v>
       </c>
       <c r="BX10" t="n">
         <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.202612912290232</v>
+        <v>5.2774032242362e-05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0.03949914386459753</v>
+        <v>0.08445719409614343</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,25 +5794,25 @@
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.02856842039815325</v>
+        <v>0.02583726468647647</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0.04584592059462468</v>
+        <v>0.05150359414549655</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.02716642259282045</v>
+        <v>0.05639021060146186</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.03071314587756911</v>
+        <v>0.05856149153730772</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5821,241 +5821,241 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.02299985259838213</v>
+        <v>-0.07021663802454602</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.007112116121463358</v>
+        <v>0.02536462897495289</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.07315215811266733</v>
+        <v>-0.03490185649961067</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0.0002022282476589621</v>
+        <v>0.01549608234402804</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01618311959948777</v>
+        <v>0.04101478735022961</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0.04126077516050915</v>
+        <v>-0.0008604480428880209</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.002597102713438232</v>
+        <v>0.009625381774029806</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.03513433173036249</v>
+        <v>0.02548893170592722</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.02693819873231675</v>
+        <v>-0.004591293257282808</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0.04634927981621421</v>
+        <v>-0.02733946696656818</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01756772099881736</v>
+        <v>0.1481393656135003</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.03086334235184199</v>
+        <v>0.004874902778597682</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.04672021279145865</v>
+        <v>-0.1101474370146151</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01720663536355539</v>
+        <v>0.02058835383823784</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.02785344536350228</v>
+        <v>-0.1556779831055027</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.03704616916294061</v>
+        <v>-0.07639707044660794</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.007419994549347245</v>
+        <v>0.1878937417740311</v>
       </c>
       <c r="DX10" t="n">
         <v>0</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.02875219393831091</v>
+        <v>0.02724398256129587</v>
       </c>
       <c r="DZ10" t="n">
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.04670147497510798</v>
+        <v>-0.1250453319197187</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0.000153701711460362</v>
+        <v>-0.02911554247104382</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.006162976908483303</v>
+        <v>-0.02396431078190454</v>
       </c>
       <c r="EG10" t="n">
         <v>0</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0.1036142042218878</v>
+        <v>0.02080509437160711</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05203926089574881</v>
+        <v>-0.02372121228815167</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.008460449785937598</v>
+        <v>0.1777852068877007</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01057927985086754</v>
+        <v>0.2318792613578783</v>
       </c>
       <c r="EP10" t="n">
         <v>0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0.01628850735478286</v>
+        <v>0.06580917201729038</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.0535392394240689</v>
+        <v>0.03763099857385058</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0.003424427519302957</v>
+        <v>0.1066714249669298</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01768019578167852</v>
+        <v>0.009253149922380036</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0.04494425053755952</v>
+        <v>-0.01876375012442819</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01816987194153631</v>
+        <v>0.02746674829053386</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.03335754188693371</v>
+        <v>0.03233286925976919</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01269324761613692</v>
+        <v>0.2707803748897645</v>
       </c>
       <c r="FH10" t="n">
         <v>-0</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0.0007987069427005477</v>
+        <v>-0.02390015126368373</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.009377133278481633</v>
+        <v>0.1074154459456965</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0.03972998865588775</v>
+        <v>0.0007216115273652666</v>
       </c>
       <c r="FN10" t="n">
         <v>0</v>
@@ -6064,40 +6064,40 @@
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.02964507365166902</v>
+        <v>0.1509156750672532</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.04120901913544261</v>
+        <v>-0.185869367644697</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.06880846960483501</v>
+        <v>0.03174108290882077</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.02086565287695602</v>
+        <v>-0.03432593910821553</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.02150627269762451</v>
+        <v>0.0921532052673826</v>
       </c>
       <c r="FZ10" t="n">
         <v>-0</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.00414362987797256</v>
+        <v>0.05157286435907781</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,16 +6106,16 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0.02244547011170255</v>
+        <v>-0.04497803009865811</v>
       </c>
       <c r="GF10" t="n">
         <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1259807333601117</v>
+        <v>0.7485888270410712</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02301937546483914</v>
+        <v>-0.03154394039903792</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08581315387856449</v>
+        <v>-0.327812456584355</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09748609234614791</v>
+        <v>0.8608561536436276</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01647224901781712</v>
+        <v>-0.2389113881682247</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.07542484894716346</v>
+        <v>-0.2826258792510667</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,76 +6177,76 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01815649936774794</v>
+        <v>0.1684134042282826</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01167744740018464</v>
+        <v>-0.09333683073836599</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01308893186328479</v>
+        <v>-0.09947597636657406</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02124544115510041</v>
+        <v>0.07970450818309904</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01570383282279056</v>
+        <v>-0.2773991641900265</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01242289551271871</v>
+        <v>-0.09129241604737567</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.01051367626247591</v>
+        <v>0.2461253951407762</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.007078499889254015</v>
+        <v>0.01734978865409225</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04333289229419343</v>
+        <v>-0.2253258436050637</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1066469265611727</v>
+        <v>1.137046614406864</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.002832920522001366</v>
+        <v>-0.4089961014611148</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.07863699671722171</v>
+        <v>-0.3442119419276007</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05982816657989944</v>
+        <v>-0.07154062635405299</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.03497832534825539</v>
+        <v>-0.09629277987963024</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.04485198471978241</v>
+        <v>-0.1702422344650763</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04165054483651519</v>
+        <v>0.1778517166142442</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01658229702873098</v>
+        <v>0.1648549924862485</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.008553383750207671</v>
+        <v>0.03934160353380405</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.05497981887600373</v>
+        <v>0.7367960391778594</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01025617373814926</v>
+        <v>-0.1354832880814523</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.03952080270429321</v>
+        <v>-0.3150609936810786</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6363,25 +6363,25 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02969030730933977</v>
+        <v>-0.3301633337054934</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001415961895782184</v>
+        <v>0.05707832167794442</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02396474727452016</v>
+        <v>0.194826188176856</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,49 +6393,49 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.007102225870887156</v>
+        <v>-0.2654373389385742</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.00123468192209517</v>
+        <v>0.1617135493650636</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.006264636836106673</v>
+        <v>0.1342572460115666</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02331535123478067</v>
+        <v>-0.3187754291454848</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.001550318815285936</v>
+        <v>0.008676255209345785</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02777984056282974</v>
+        <v>0.1860146873038674</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01109436781000972</v>
+        <v>-0.04511191605811486</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0102775413737261</v>
+        <v>-0.1044474135680057</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02860249517489055</v>
+        <v>0.03241572062156348</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.008657518566327729</v>
+        <v>-0.1308411373638692</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03496376121616514</v>
+        <v>-0.02651203575025356</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0003430155950841797</v>
+        <v>0.1331465702118974</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6495,52 +6495,52 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.03113114938514686</v>
+        <v>0.05107690113018862</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
         <v>0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0100656492026086</v>
+        <v>-0.03791194157476764</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01342476963610098</v>
+        <v>-0.0465651192214752</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.01900929513019758</v>
+        <v>-0.08504154977867413</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.006235848460082736</v>
+        <v>-0.1216090037645003</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.006940470488230846</v>
+        <v>0.1074501919569272</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6549,67 +6549,67 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.009401322862424734</v>
+        <v>-0.218782593625664</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01165856675682221</v>
+        <v>-0.05070146949274418</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01706466590410159</v>
+        <v>0.07350308013112564</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02445884056529072</v>
+        <v>-0.34849665544583</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.006486081437289151</v>
+        <v>-0.005688808966205101</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02873229378686575</v>
+        <v>0.169346046896088</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.001219238720694797</v>
+        <v>-0.320907611195214</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,13 +6618,13 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02345380623643031</v>
+        <v>0.1013438232539745</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03328554585826819</v>
+        <v>0.1820326133900682</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.007729298666214851</v>
+        <v>-0.1614074764795973</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,46 +6645,46 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.009427304773750422</v>
+        <v>0.05764650029536084</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.001213185668404891</v>
+        <v>-0.006551179121902204</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01553979355634512</v>
+        <v>-0.1438594048568378</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.0365565510022353</v>
+        <v>-0.009059222080185413</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,19 +6692,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4370842760053621</v>
+        <v>0.2842314806282829</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1741296236417095</v>
+        <v>-0.2890632864168471</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1582820569784088</v>
+        <v>0.01885019897500148</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6719,16 +6719,16 @@
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3801920519853615</v>
+        <v>0.2911901425269863</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1671028522051645</v>
+        <v>-0.3393978699607442</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1774863071115594</v>
+        <v>0.01319425975164435</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.09309674698792475</v>
+        <v>0.09536449121405381</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0360002653715732</v>
+        <v>-0.04314419866159418</v>
       </c>
       <c r="W12" t="n">
-        <v>0.07201651147374044</v>
+        <v>-0.1751718137475589</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,25 +6770,25 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1422469761750964</v>
+        <v>-0.02054601969857438</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.005973454495070292</v>
+        <v>-0.1034161668096515</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.004517758523531985</v>
+        <v>-0.1094891168913263</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,46 +6797,46 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02239730769743459</v>
+        <v>0.1588600167699696</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04164771337476206</v>
+        <v>-0.04558679423841275</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.09484296920906947</v>
+        <v>0.05501472788926987</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5054440680354074</v>
+        <v>0.394193026880529</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.0621019814080568</v>
+        <v>-0.1218231809163978</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.007534925546275908</v>
+        <v>-0.2610306581177207</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.08072219145558869</v>
+        <v>-0.114027300978932</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.09710005877592084</v>
+        <v>-0.09824477558414031</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1398758339933191</v>
+        <v>-0.09045657542556113</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1323844144330903</v>
+        <v>0.02455227959113999</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0665949814058109</v>
+        <v>0.07766220214069335</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1631490508231854</v>
+        <v>0.04250225653938533</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3009975507039233</v>
+        <v>0.2928284880102572</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.07022886576382249</v>
+        <v>-0.2008702514891466</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0590307998367834</v>
+        <v>-0.07908190260013155</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1042755560469199</v>
+        <v>-0.1318225978246548</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.03019786213611127</v>
+        <v>0.1873451977802468</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.02357534322878754</v>
+        <v>0.02929052009796451</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,52 +6962,52 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.07429081918419181</v>
+        <v>-0.02821887910166638</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.02033787747252617</v>
+        <v>0.1526708871649675</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07895232376003369</v>
+        <v>0.1288207025662193</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09007417473117446</v>
+        <v>-0.11815956943233</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.05223949315922682</v>
+        <v>0.2019893008213573</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.01566577169192368</v>
+        <v>0.03717967835253676</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,43 +7016,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.00880365497699854</v>
+        <v>-0.006999939046016218</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1316227318078869</v>
+        <v>0.08750168296623267</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01248660227866101</v>
+        <v>-0.02335260653580277</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07690239515886216</v>
+        <v>-0.129764232267795</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.06064218562009874</v>
+        <v>0.1482996954107732</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.09975891257276459</v>
+        <v>0.01503711202040588</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7061,25 +7061,25 @@
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1365317735925978</v>
+        <v>-0.07192828447679055</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.03034659499524232</v>
+        <v>-0.09429800957936159</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.0721025289704416</v>
+        <v>-0.1651389315524904</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09060298126207531</v>
+        <v>-0.05764045745957355</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.08112203924138668</v>
+        <v>0.116712579276371</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1325908811703992</v>
+        <v>0.04675825622848464</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,43 +7124,43 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06552586126714904</v>
+        <v>-0.1101178396676858</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03863604209671648</v>
+        <v>0.1333235244881713</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.06851212717296633</v>
+        <v>-0.04534880880625455</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09040044057764737</v>
+        <v>-0.1344474827391942</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.05539673945303962</v>
+        <v>0.2046348562103265</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.03705297352348669</v>
+        <v>0.01227299920463198</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,58 +7169,58 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.1094169810494372</v>
+        <v>-0.07057157665777264</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06109829855458181</v>
+        <v>0.09407537185432945</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05369970870333072</v>
+        <v>-0.1657615769074777</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01964714358159579</v>
+        <v>-0.01521982270970098</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.03098093925463654</v>
+        <v>-0.03225369951585858</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.03974346711908143</v>
+        <v>0.07446142792979329</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
@@ -7229,16 +7229,16 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.04896156636712201</v>
+        <v>-0.1046763871144243</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03619280308855152</v>
+        <v>0.2225563598725648</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
@@ -7250,7 +7250,7 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1718189728779962</v>
+        <v>0.165131866179179</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -7267,25 +7267,25 @@
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1119981729098626</v>
+        <v>-0.2630426643800343</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1085928568610091</v>
+        <v>0.124215638824343</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1622655178038572</v>
+        <v>0.1056922933311577</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -7294,25 +7294,25 @@
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03858679198062701</v>
+        <v>-0.3361916480643498</v>
       </c>
       <c r="N13" t="n">
-        <v>0.05102244742999536</v>
+        <v>0.06074331870645954</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03645129677684913</v>
+        <v>-0.02372545639946313</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -7321,40 +7321,40 @@
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.05975966303264901</v>
+        <v>-0.05512894282906269</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04164408929765993</v>
+        <v>-0.07012011006014729</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.02148401684059368</v>
+        <v>0.0565056573895411</v>
       </c>
       <c r="AC13" t="n">
         <v>-0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01337116980043242</v>
+        <v>0.07100179731987202</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02397573194503859</v>
+        <v>0.2332234341545651</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,49 +7363,49 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.01167717167676426</v>
+        <v>0.04517947778049938</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.02216538449117626</v>
+        <v>-0.1533458409459394</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.06139862228301438</v>
+        <v>0.07125614809390311</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.1136665514123651</v>
+        <v>-0.1023291514039761</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.07444079825058575</v>
+        <v>-0.3760586655542856</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1597481966540818</v>
+        <v>-0.008203302811208126</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
@@ -7420,7 +7420,7 @@
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.1109082855224972</v>
+        <v>0.188949994081572</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -7429,37 +7429,37 @@
         <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0001911530304130537</v>
+        <v>0.2504600970586498</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.06999080378094881</v>
+        <v>0.2059071245916863</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.05241434047031007</v>
+        <v>-0.01739660878457672</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01313696484277989</v>
+        <v>0.01322693348336467</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.10505679081605</v>
+        <v>-0.1232799325530614</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -7468,25 +7468,25 @@
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.06467075305022432</v>
+        <v>-0.08107243498536233</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.01560712461637712</v>
+        <v>-0.2970574724540473</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08122569375042819</v>
+        <v>-0.06154305227850503</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.03167472754986586</v>
+        <v>-0.06674542862311038</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
@@ -7510,10 +7510,10 @@
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.01264060167983138</v>
+        <v>0.1090263869699566</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02567930385950694</v>
+        <v>-0.04379992479912813</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7528,34 +7528,34 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.02239430663506179</v>
+        <v>0.01203443229110535</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.06568911298480125</v>
+        <v>0.1004129321226968</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.07043356334040066</v>
+        <v>-0.06032828621765473</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.02175154064005948</v>
+        <v>-0.06028098601052261</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
@@ -7564,10 +7564,10 @@
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0009885559782112708</v>
+        <v>0.1114161337236192</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01470668757315542</v>
+        <v>-0.0226175027889742</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7579,10 +7579,10 @@
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.01798624950906793</v>
+        <v>-0.01730209128940065</v>
       </c>
       <c r="DF13" t="n">
         <v>-0</v>
@@ -7591,10 +7591,10 @@
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0750946527953705</v>
+        <v>0.1246365250691016</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.02641118039748334</v>
+        <v>-0.01650456029762297</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7609,79 +7609,79 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.0234958137637556</v>
+        <v>-0.08289735087765376</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.03681225530222768</v>
+        <v>0.0355191145291336</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.06655966960781814</v>
+        <v>-0.003435220388828746</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.03996376736383249</v>
+        <v>0.006279944858536026</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.02365154207226329</v>
+        <v>-0.004443775455435723</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02216878564396906</v>
+        <v>0.006613443319215155</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.02373117537508749</v>
+        <v>-0.09587528624961088</v>
       </c>
       <c r="EG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01487067321483362</v>
+        <v>0.09571653557290222</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.009434749953873977</v>
+        <v>0.01698120052546524</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.009614901561347231</v>
+        <v>0.03574875710475686</v>
       </c>
       <c r="EP13" t="n">
         <v>0</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0199044463827133</v>
+        <v>0.1425640730327049</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.006426188200675419</v>
+        <v>0.005897189506592082</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7717,19 +7717,19 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.02267507688106702</v>
+        <v>-0.06622805735192894</v>
       </c>
       <c r="EY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.008291494852606208</v>
+        <v>0.1535068004318583</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.02507287181457483</v>
+        <v>-0.03133767395452739</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0.01577414788270292</v>
+        <v>0.02905031501430139</v>
       </c>
       <c r="FH13" t="n">
         <v>0</v>
@@ -7753,10 +7753,10 @@
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.02393219954718961</v>
+        <v>0.130542591699813</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1173181824528978</v>
+        <v>0.1429596391412251</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
@@ -7765,55 +7765,55 @@
         <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.006845432113405612</v>
+        <v>-0.002414879457281568</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.004880586868035616</v>
+        <v>0.2508740050730966</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0499783088954413</v>
+        <v>0.06251240196299118</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02229574876643774</v>
+        <v>0.02238019072223139</v>
       </c>
       <c r="FZ13" t="n">
         <v>0</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.019358411645213</v>
+        <v>0.2192448718999084</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -8968,25 +8968,25 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.464006037743842</v>
+        <v>0.314145788800321</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.213690755922597</v>
+        <v>-0.2630150233388923</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05623636678274033</v>
+        <v>-0.04154194224357333</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,22 +8995,22 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3091686772893197</v>
+        <v>0.3346466621589709</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2493368450749698</v>
+        <v>-0.3735854753679781</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0678724014983766</v>
+        <v>-0.1534833559616527</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9022,76 +9022,76 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.09973576278518753</v>
+        <v>0.04239057501050498</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.00436861355272419</v>
+        <v>-0.07294956953102974</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1397611844091128</v>
+        <v>-0.1039332299772386</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.08363278850976616</v>
+        <v>-0.06682054282775272</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.03235867436458721</v>
+        <v>-0.1338630572404317</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.04178331435940076</v>
+        <v>-0.1111889495151816</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.01050531881593712</v>
+        <v>0.1179148448985517</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.06186637562024456</v>
+        <v>-0.1377015329322635</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01192210134947837</v>
+        <v>0.0439053542363767</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9103,25 +9103,25 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.3966580425402422</v>
+        <v>0.2855782200138257</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.06127107439789742</v>
+        <v>-0.08313622975428614</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1306370379137497</v>
+        <v>-0.2868230995938325</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,25 +9130,25 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05347188316916103</v>
+        <v>-0.003958388697119392</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.2043371808784797</v>
+        <v>-0.03629547620714586</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1681918769594767</v>
+        <v>0.0001280487735494992</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,100 +9157,100 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1016645978499683</v>
+        <v>0.01919082380468094</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0.0001228360759275198</v>
+        <v>0.0864378286743905</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1742894553249103</v>
+        <v>0.0411381760555535</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1625996662776479</v>
+        <v>0.1935117731056679</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.03388422312014398</v>
+        <v>-0.177872122119126</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.111371108770046</v>
+        <v>-0.08123479082683041</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.09082279854626153</v>
+        <v>-0.09253252183449084</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.005380913520061375</v>
+        <v>0.1395649095756381</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01251183687505771</v>
+        <v>0.02445692973514838</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.004471039862110992</v>
+        <v>-0.05299729123237797</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.1611631133197839</v>
+        <v>0.2214959968904062</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.07520678045576151</v>
+        <v>0.08158954412880533</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,22 +9259,22 @@
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.06708394399390694</v>
+        <v>-0.09133530370410042</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.03345121933472785</v>
+        <v>0.1498347754292303</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.0207512881300389</v>
+        <v>0.03738589086240092</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9283,25 +9283,25 @@
         <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.02276686092105686</v>
+        <v>-0.05329882527686556</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.05207944114056191</v>
+        <v>0.04766981810766879</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02337216052914406</v>
+        <v>-0.108959657820695</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,28 +9316,28 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03742764311262105</v>
+        <v>-0.07721900347951557</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.006384190694356076</v>
+        <v>-0.05025921361606409</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.02685428571379275</v>
+        <v>0.01445738803957813</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,43 +9346,43 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.04277621502120528</v>
+        <v>0.003240517300027538</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.03336448705702407</v>
+        <v>0.08065633073837666</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.0598049975572133</v>
+        <v>-0.03292810342281537</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.0821178888512053</v>
+        <v>-0.04641045118374427</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0.006177931725444511</v>
+        <v>0.09254687899837809</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.07160918356618702</v>
+        <v>0.06485023233454647</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
@@ -9394,22 +9394,22 @@
         <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01779063133182174</v>
+        <v>-0.007266316837973302</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.02072505532524003</v>
+        <v>0.1090937149759125</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.01708695067292624</v>
+        <v>-0.04375244540309369</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9424,28 +9424,28 @@
         <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.06403190689084767</v>
+        <v>-0.09736494345671873</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.004942794769620109</v>
+        <v>0.1746218877951349</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.0005639592097789705</v>
+        <v>0.01246709101308247</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
         <v>0</v>
@@ -9454,16 +9454,16 @@
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.004321361019999555</v>
+        <v>0.125077116228017</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.01939565078559337</v>
+        <v>0.10757702137438</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.003135083571775055</v>
+        <v>-0.01407417221039569</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
@@ -9472,58 +9472,58 @@
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.02165836749609637</v>
+        <v>0.03496786334179784</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.05039422313082665</v>
+        <v>0.1584954460029219</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.03165644400317966</v>
+        <v>-0.02622348279367825</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.05240979100968161</v>
+        <v>0.005008782147926162</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.1042547420564951</v>
+        <v>0.07283237799855399</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2236901653674261</v>
+        <v>0.3001322921636938</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,25 +9546,25 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05706061209626856</v>
+        <v>-0.09135508956989125</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1617953627012015</v>
+        <v>-0.1319340739498126</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1894659379273365</v>
+        <v>0.3535880951010277</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,16 +9573,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03440012274583153</v>
+        <v>-0.1661039552421609</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1572062772066234</v>
+        <v>-0.1704022747110988</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01877541559012363</v>
+        <v>0.0849127845967244</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01920831889176585</v>
+        <v>-0.08580655888182631</v>
       </c>
       <c r="X17" t="n">
-        <v>0.009138828299600209</v>
+        <v>-0.01314652604439954</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.00848575968395603</v>
+        <v>-0.03109536897300313</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.02742348770272005</v>
+        <v>-0.1913024772993715</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002690648894797191</v>
+        <v>0.05869339158131007</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.02408351570625542</v>
+        <v>0.0261588855561148</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
@@ -9654,13 +9654,13 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.005351731095185492</v>
+        <v>-0.05513934396092914</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.02687203259610787</v>
+        <v>0.007218524906040805</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,10 +9669,10 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1507701256935356</v>
+        <v>0.325403788038968</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,13 +9681,13 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.02255599841015753</v>
+        <v>-0.2849790876054651</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.05540035372147048</v>
+        <v>-0.1081432161501736</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
         <v>-0</v>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.05177891918719758</v>
+        <v>-0.02083280208588419</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,52 +9708,52 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.0591959157212214</v>
+        <v>-0.002289110482997798</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.07844582386224749</v>
+        <v>-0.0158573346596869</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.05058529276217728</v>
+        <v>0.04296811656162763</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01499947708081137</v>
+        <v>0.07367428613705772</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01835980282120872</v>
+        <v>0.001271637541390187</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.07648627615069933</v>
+        <v>0.1835113648794773</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02136754829659425</v>
+        <v>-0.09442367329778883</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.03302888841011239</v>
+        <v>-0.08767966675369208</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9774,28 +9774,28 @@
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.03589458903815913</v>
+        <v>-0.07971635082407591</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.002269519853894627</v>
+        <v>0.05636328192540326</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.03804311726017649</v>
+        <v>0.03991224878989466</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,46 +9807,46 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.0008833799638143314</v>
+        <v>-0.07430892715676077</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0005760952829363495</v>
+        <v>0.1648058136748959</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.0282599015719155</v>
+        <v>0.04995210890273311</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.02875121916033409</v>
+        <v>-0.0822749848321611</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.0007255696105070718</v>
+        <v>0.0491636997255585</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.03768351293579356</v>
+        <v>0.06189966806030817</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9861,61 +9861,61 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01453064425495513</v>
+        <v>-0.01687385474716499</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02416277996837621</v>
+        <v>-0.07884678407686009</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.005194844261149644</v>
+        <v>0.04428853090956416</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.006998714500046086</v>
+        <v>-0.007331338967655068</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01749878985250384</v>
+        <v>-0.04896019345731065</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.007969609502787918</v>
+        <v>0.01156828736014513</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.03712041572962683</v>
+        <v>0.007334845666263781</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,124 +9924,124 @@
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01241889268291696</v>
+        <v>-0.002517558847856746</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.01743653030606074</v>
+        <v>0.004172812544999852</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.0396685130155616</v>
+        <v>-0.04088749416789738</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
         <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.008875487575524388</v>
+        <v>0.04928649703502855</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.03571096574975172</v>
+        <v>0.002591240419361371</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO17" t="n">
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01226075680706109</v>
+        <v>-0.01101919938868806</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.009776754541435605</v>
+        <v>0.0005804424173340167</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.02035008030565537</v>
+        <v>0.06598920450031359</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.02847507285626069</v>
+        <v>-0.09515425465040804</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.001882318909216545</v>
+        <v>0.03893302414733084</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.03905761169621512</v>
+        <v>0.03423806547610069</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01241297234233389</v>
+        <v>0.1516319441997835</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.001274956631300459</v>
+        <v>-0.08911261657924267</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.02248705960427439</v>
+        <v>0.08228287976847067</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,46 +10050,46 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.009821790994192531</v>
+        <v>0.06475810057214321</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.02405241553919783</v>
+        <v>-0.1204972415412001</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.02105405408501342</v>
+        <v>-0.01791404398405924</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0116913527863489</v>
+        <v>-0.04511954878923748</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.02008225222196747</v>
+        <v>0.07989598954662305</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
@@ -10098,7 +10098,7 @@
         <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,22 +10106,22 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4782714593545428</v>
+        <v>0.2787697413280091</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1894115948988301</v>
+        <v>-0.2562016884638672</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09490629691274956</v>
+        <v>-0.0390825857985256</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10133,16 +10133,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3054795686575793</v>
+        <v>0.2961233514432616</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2197097344254202</v>
+        <v>-0.3339087059594285</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09949893958016359</v>
+        <v>-0.1206789739700246</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -10154,82 +10154,82 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1077960096535445</v>
+        <v>0.04939615563797634</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.006828486107908502</v>
+        <v>-0.05870504833904768</v>
       </c>
       <c r="W18" t="n">
-        <v>0.09388041128651994</v>
+        <v>-0.07736894678672469</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.05856527514848074</v>
+        <v>-0.06924667145094</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.01073816182508737</v>
+        <v>-0.1205968490127256</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.01830959913707527</v>
+        <v>-0.08829266054450023</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01287809739128203</v>
+        <v>0.0966971677690404</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.0589707505191921</v>
+        <v>-0.107514901345928</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.05266308354040482</v>
+        <v>0.02487839446953209</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10241,25 +10241,25 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.3955811274091116</v>
+        <v>0.2427157928301581</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.03227531954540133</v>
+        <v>-0.09519385881972617</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.08510792053750782</v>
+        <v>-0.2390413670597198</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,25 +10268,25 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02417466746100158</v>
+        <v>-0.007896421841567794</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.1882588326087855</v>
+        <v>-0.05762712830362857</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1222923605297916</v>
+        <v>0.009771889395360835</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
@@ -10295,19 +10295,19 @@
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.1533617734419133</v>
+        <v>0.03014638008469126</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.04130492429331169</v>
+        <v>0.07552079533560024</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1641448300559005</v>
+        <v>0.03995745653928606</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
         <v>0</v>
@@ -10316,85 +10316,85 @@
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1844227469771434</v>
+        <v>0.1544431758830736</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.01822151604457413</v>
+        <v>-0.1484496519527016</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.05605173382089629</v>
+        <v>-0.06450638767352505</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.07923880815693203</v>
+        <v>-0.06227530183812247</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.004831706402358455</v>
+        <v>0.1233851424323814</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.004544984842683445</v>
+        <v>0.02050600238500529</v>
       </c>
       <c r="CI18" t="n">
         <v>-0</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01574379932668527</v>
+        <v>-0.05167269093715902</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.08951030982185573</v>
+        <v>0.1957251092383614</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.08893722397694123</v>
+        <v>0.06693215239769025</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
         <v>-0</v>
@@ -10403,43 +10403,43 @@
         <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.05251758135050987</v>
+        <v>-0.06100184200581311</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.03457433797983273</v>
+        <v>0.1291003131840144</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.01279026147411001</v>
+        <v>0.02886042133822795</v>
       </c>
       <c r="DA18" t="n">
         <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.04505374610212851</v>
+        <v>-0.07876833667303913</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.03943452991075673</v>
+        <v>0.0295246829344965</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.03326546437488605</v>
+        <v>-0.03229007108705032</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
@@ -10454,28 +10454,28 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.04342295432720455</v>
+        <v>-0.05343621754597525</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.01135203416512043</v>
+        <v>-0.02422208438085761</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.03556450625359007</v>
+        <v>-0.001139233054871698</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>0</v>
@@ -10484,16 +10484,16 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.09779877077169984</v>
+        <v>0.03853368331197899</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0.01483689547975089</v>
+        <v>0.08663854317643559</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.04032926498103225</v>
+        <v>-0.0829599092134749</v>
       </c>
       <c r="EB18" t="n">
         <v>-0</v>
@@ -10505,55 +10505,55 @@
         <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.06771867336228811</v>
+        <v>-0.02836909565790375</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.015212052951692</v>
+        <v>0.08588784125485617</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.05665713826190658</v>
+        <v>0.05177194517823833</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.0002038601761399163</v>
+        <v>-0.008255728819407518</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.0002849429368399326</v>
+        <v>0.09346798494054351</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.03778278063671914</v>
+        <v>-0.02382320754177679</v>
       </c>
       <c r="ET18" t="n">
         <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10562,25 +10562,25 @@
         <v>-0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.05089368823424342</v>
+        <v>-0.06978839110742938</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.001197502785281838</v>
+        <v>0.1526749685896442</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.01542012996633939</v>
+        <v>0.008645321512134001</v>
       </c>
       <c r="FC18" t="n">
         <v>-0</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
@@ -10592,16 +10592,16 @@
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.06070096715971212</v>
+        <v>0.1299822643010408</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.004776559500658016</v>
+        <v>0.09274991753879444</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.04627201818263581</v>
+        <v>-0.06604358025352582</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10610,31 +10610,31 @@
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.04319925203532338</v>
+        <v>0.04807682952170628</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.02396726819214683</v>
+        <v>0.1695312302705575</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.0518789332825917</v>
+        <v>-0.05191771399308842</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW18" t="n">
         <v>0</v>
@@ -10643,25 +10643,25 @@
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.05615709330700719</v>
+        <v>0.01759791951194175</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.1078446001861136</v>
+        <v>0.04180810623934257</v>
       </c>
       <c r="GC18" t="n">
         <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
         <v>0</v>
